--- a/Progetto/versione_ibrida/previsioni_biodeg.xlsx
+++ b/Progetto/versione_ibrida/previsioni_biodeg.xlsx
@@ -15865,7 +15865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15912,151 +15912,163 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Soglia ROC ottimale (Youden's J) = 0.4093</t>
+          <t>Metodo Ibrido – Soglia ROC (Youden's J) su ŷ colonna Biodeg</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. Componenti Latenti (LV)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
+          <t>Soglia ROC (Youden's J)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.4093</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. Variabili</t>
+          <t>N. Componenti Latenti (LV)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Strategia selezione variabili</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>VIP &gt; 1</t>
-        </is>
+          <t>N. Variabili</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Variabili utilizzate</t>
+          <t>Strategia selezione variabili</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SpMax_L, HyWi_B(m), LOC, nO, SM6_L, Mi, SpPosA_B(p), nCIR, F04[C-N], SpMax_A, C%</t>
+          <t>VIP &gt; 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cross-Validation</t>
+          <t>Variabili utilizzate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stratified 10-Fold</t>
+          <t>SpMax_L, HyWi_B(m), LOC, nO, SM6_L, Mi, SpPosA_B(p), nCIR, F04[C-N], SpMax_A, C%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Balanced Accuracy (CV)</t>
+          <t>Cross-Validation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.8575</t>
+          <t>Stratified 10-Fold</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Balanced Accuracy (Test)</t>
+          <t>Balanced Accuracy (CV)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.8343</t>
+          <t>0.8575</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sensitivity (Test)</t>
+          <t>Balanced Accuracy (Test)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.8056</t>
+          <t>0.8343</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Specificity (Test)</t>
+          <t>Sensitivity (Test)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.8630</t>
+          <t>0.8056</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. campioni Training</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>837</v>
+          <t>Specificity (Test)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.8630</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. campioni Test</t>
+          <t>N. campioni Training</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>218</v>
+        <v>837</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. campioni Xeval</t>
+          <t>N. campioni Test</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>670</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>N. campioni Xeval</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Campioni Xeval fuori dominio</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>33 / 670 (4.9%)</t>
         </is>
